--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122407517</v>
+        <v>122409149</v>
       </c>
       <c r="B2" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454420</v>
+        <v>454455</v>
       </c>
       <c r="R2" t="n">
-        <v>6754420</v>
+        <v>6754359</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122409149</v>
+        <v>122407709</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454455</v>
+        <v>454420</v>
       </c>
       <c r="R3" t="n">
-        <v>6754359</v>
+        <v>6754420</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>122406658</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122410095</v>
+        <v>122408531</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,42 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454463</v>
+        <v>454354</v>
       </c>
       <c r="R5" t="n">
-        <v>6754144</v>
+        <v>6754279</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122408531</v>
+        <v>122410095</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,37 +1343,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454354</v>
+        <v>454463</v>
       </c>
       <c r="R8" t="n">
-        <v>6754279</v>
+        <v>6754144</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1417,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,15 +1437,135 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122410135</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56584</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>454406</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6754542</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Göran Ehn</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Göran Ehn</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122409149</v>
+        <v>122408664</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454455</v>
+        <v>454418</v>
       </c>
       <c r="R2" t="n">
-        <v>6754359</v>
+        <v>6754374</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,9 +748,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122406658</v>
+        <v>122408874</v>
       </c>
       <c r="B4" t="n">
         <v>78646</v>
@@ -925,17 +930,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454390</v>
+        <v>454455</v>
       </c>
       <c r="R4" t="n">
-        <v>6754454</v>
+        <v>6754359</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,19 +967,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1113,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122408664</v>
+        <v>122409149</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,37 +1124,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454418</v>
+        <v>454455</v>
       </c>
       <c r="R6" t="n">
-        <v>6754374</v>
+        <v>6754359</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,19 +1186,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,19 +1203,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122408874</v>
+        <v>122406658</v>
       </c>
       <c r="B7" t="n">
         <v>78646</v>
@@ -1261,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R7" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,9 +1288,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1315,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410095</v>
+        <v>122410135</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>56584</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,46 +1339,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454463</v>
+        <v>454406</v>
       </c>
       <c r="R8" t="n">
-        <v>6754144</v>
+        <v>6754542</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,12 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,22 +1435,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122410135</v>
+        <v>122410095</v>
       </c>
       <c r="B9" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,49 +1459,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454406</v>
+        <v>454463</v>
       </c>
       <c r="R9" t="n">
-        <v>6754542</v>
+        <v>6754144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1537,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122408664</v>
+        <v>122408874</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454418</v>
+        <v>454455</v>
       </c>
       <c r="R2" t="n">
-        <v>6754374</v>
+        <v>6754359</v>
       </c>
       <c r="S2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122407709</v>
+        <v>122409149</v>
       </c>
       <c r="B3" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454420</v>
+        <v>454455</v>
       </c>
       <c r="R3" t="n">
-        <v>6754420</v>
+        <v>6754359</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122408874</v>
+        <v>122408531</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454455</v>
+        <v>454354</v>
       </c>
       <c r="R4" t="n">
-        <v>6754359</v>
+        <v>6754279</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,9 +957,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122408531</v>
+        <v>122408664</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454354</v>
+        <v>454418</v>
       </c>
       <c r="R5" t="n">
-        <v>6754279</v>
+        <v>6754374</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122409149</v>
+        <v>122406658</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,42 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R6" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,9 +1181,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122406658</v>
+        <v>122407709</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,37 +1236,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454390</v>
+        <v>454420</v>
       </c>
       <c r="R7" t="n">
-        <v>6754454</v>
+        <v>6754420</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,19 +1293,14 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:44</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,12 +1315,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
         <v>122410135</v>
       </c>
       <c r="B8" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>122410095</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122408874</v>
+        <v>122408531</v>
       </c>
       <c r="B2" t="n">
         <v>78651</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454455</v>
+        <v>454354</v>
       </c>
       <c r="R2" t="n">
-        <v>6754359</v>
+        <v>6754279</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122409149</v>
+        <v>122406658</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R3" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,9 +860,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122408531</v>
+        <v>122407709</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454354</v>
+        <v>454420</v>
       </c>
       <c r="R4" t="n">
-        <v>6754279</v>
+        <v>6754420</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +972,14 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:03</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +994,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122408664</v>
+        <v>122408874</v>
       </c>
       <c r="B5" t="n">
         <v>78651</v>
@@ -1032,17 +1042,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454418</v>
+        <v>454455</v>
       </c>
       <c r="R5" t="n">
-        <v>6754374</v>
+        <v>6754359</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,19 +1079,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,19 +1096,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122406658</v>
+        <v>122408664</v>
       </c>
       <c r="B6" t="n">
         <v>78651</v>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454390</v>
+        <v>454418</v>
       </c>
       <c r="R6" t="n">
-        <v>6754454</v>
+        <v>6754374</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122407709</v>
+        <v>122409149</v>
       </c>
       <c r="B7" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,34 +1236,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454420</v>
+        <v>454455</v>
       </c>
       <c r="R7" t="n">
-        <v>6754420</v>
+        <v>6754359</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1296,11 +1301,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410135</v>
+        <v>122410095</v>
       </c>
       <c r="B8" t="n">
-        <v>56589</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,49 +1339,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454406</v>
+        <v>454463</v>
       </c>
       <c r="R8" t="n">
-        <v>6754542</v>
+        <v>6754144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1417,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,22 +1437,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122410095</v>
+        <v>122410135</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>56589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,46 +1461,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454463</v>
+        <v>454406</v>
       </c>
       <c r="R9" t="n">
-        <v>6754144</v>
+        <v>6754542</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,12 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122408531</v>
+        <v>122409149</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454354</v>
+        <v>454455</v>
       </c>
       <c r="R2" t="n">
-        <v>6754279</v>
+        <v>6754359</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122406658</v>
+        <v>122407709</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +793,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454390</v>
+        <v>454420</v>
       </c>
       <c r="R3" t="n">
-        <v>6754454</v>
+        <v>6754420</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +845,14 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:44</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122407709</v>
+        <v>122406658</v>
       </c>
       <c r="B4" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +895,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454420</v>
+        <v>454390</v>
       </c>
       <c r="R4" t="n">
-        <v>6754420</v>
+        <v>6754454</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,14 +947,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lunglav på äldre sälg.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122408874</v>
+        <v>122408531</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,11 +1004,6 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1042,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454455</v>
+        <v>454354</v>
       </c>
       <c r="R5" t="n">
-        <v>6754359</v>
+        <v>6754279</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,9 +1054,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122408664</v>
+        <v>122408874</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,11 +1111,6 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1144,17 +1124,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454418</v>
+        <v>454455</v>
       </c>
       <c r="R6" t="n">
-        <v>6754374</v>
+        <v>6754359</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,19 +1161,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122409149</v>
+        <v>122408664</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,42 +1206,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454455</v>
+        <v>454418</v>
       </c>
       <c r="R7" t="n">
-        <v>6754359</v>
+        <v>6754374</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,9 +1258,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410095</v>
+        <v>122410135</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>56589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,46 +1309,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454463</v>
+        <v>454406</v>
       </c>
       <c r="R8" t="n">
-        <v>6754144</v>
+        <v>6754542</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1375,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,12 +1385,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,22 +1400,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122410135</v>
+        <v>122410095</v>
       </c>
       <c r="B9" t="n">
-        <v>56589</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,49 +1424,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454406</v>
+        <v>454463</v>
       </c>
       <c r="R9" t="n">
-        <v>6754542</v>
+        <v>6754144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1487,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1497,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1517,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122409149</v>
+        <v>122408664</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454455</v>
+        <v>454418</v>
       </c>
       <c r="R2" t="n">
-        <v>6754359</v>
+        <v>6754374</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122407709</v>
+        <v>122407517</v>
       </c>
       <c r="B3" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +804,11 @@
       </c>
       <c r="E3" t="n">
         <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -879,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122406658</v>
+        <v>122408874</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,6 +912,11 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -910,17 +930,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454390</v>
+        <v>454455</v>
       </c>
       <c r="R4" t="n">
-        <v>6754454</v>
+        <v>6754359</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +967,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122408531</v>
+        <v>122409149</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,32 +1012,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454354</v>
+        <v>454455</v>
       </c>
       <c r="R5" t="n">
-        <v>6754279</v>
+        <v>6754359</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1074,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122408874</v>
+        <v>122406658</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,6 +1121,11 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1124,17 +1139,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R6" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,9 +1176,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122408664</v>
+        <v>122408531</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1208,6 +1233,11 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1221,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454418</v>
+        <v>454354</v>
       </c>
       <c r="R7" t="n">
-        <v>6754374</v>
+        <v>6754279</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1270,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1315,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1300,7 +1330,7 @@
         <v>122410135</v>
       </c>
       <c r="B8" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,6 +1344,11 @@
       </c>
       <c r="E8" t="n">
         <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1415,7 +1450,7 @@
         <v>122410095</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,6 +1464,11 @@
       </c>
       <c r="E9" t="n">
         <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122407517</v>
+        <v>122407709</v>
       </c>
       <c r="B3" t="n">
         <v>79737</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122408874</v>
+        <v>122409149</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,24 +910,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långsisdammen, Dlr</t>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122409149</v>
+        <v>122406658</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,42 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R5" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,9 +1074,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,19 +1101,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122406658</v>
+        <v>122408531</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1139,17 +1149,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454390</v>
+        <v>454354</v>
       </c>
       <c r="R6" t="n">
-        <v>6754454</v>
+        <v>6754279</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122408531</v>
+        <v>122408874</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1251,17 +1261,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454354</v>
+        <v>454455</v>
       </c>
       <c r="R7" t="n">
-        <v>6754279</v>
+        <v>6754359</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,19 +1298,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1315,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410135</v>
+        <v>122410095</v>
       </c>
       <c r="B8" t="n">
-        <v>56593</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,49 +1339,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454406</v>
+        <v>454463</v>
       </c>
       <c r="R8" t="n">
-        <v>6754542</v>
+        <v>6754144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1417,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,22 +1437,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122410095</v>
+        <v>122410135</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>56593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,46 +1461,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454463</v>
+        <v>454406</v>
       </c>
       <c r="R9" t="n">
-        <v>6754144</v>
+        <v>6754542</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,12 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122408664</v>
+        <v>122408531</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454418</v>
+        <v>454354</v>
       </c>
       <c r="R2" t="n">
-        <v>6754374</v>
+        <v>6754279</v>
       </c>
       <c r="S2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122407709</v>
+        <v>122407517</v>
       </c>
       <c r="B3" t="n">
         <v>79737</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122406658</v>
+        <v>122408874</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1037,17 +1037,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454390</v>
+        <v>454455</v>
       </c>
       <c r="R5" t="n">
-        <v>6754454</v>
+        <v>6754359</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1074,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122408531</v>
+        <v>122408664</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1149,17 +1139,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454354</v>
+        <v>454418</v>
       </c>
       <c r="R6" t="n">
-        <v>6754279</v>
+        <v>6754374</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,19 +1203,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122408874</v>
+        <v>122406658</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1261,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R7" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,9 +1288,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1315,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410095</v>
+        <v>122410135</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>56593</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,46 +1339,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454463</v>
+        <v>454406</v>
       </c>
       <c r="R8" t="n">
-        <v>6754144</v>
+        <v>6754542</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,12 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,22 +1435,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122410135</v>
+        <v>122410095</v>
       </c>
       <c r="B9" t="n">
-        <v>56593</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,49 +1459,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454406</v>
+        <v>454463</v>
       </c>
       <c r="R9" t="n">
-        <v>6754542</v>
+        <v>6754144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1537,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122407517</v>
+        <v>122407709</v>
       </c>
       <c r="B3" t="n">
         <v>79737</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122409149</v>
+        <v>122406658</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R4" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,9 +967,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,12 +994,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122406658</v>
+        <v>122409149</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,37 +1236,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454390</v>
+        <v>454455</v>
       </c>
       <c r="R7" t="n">
-        <v>6754454</v>
+        <v>6754359</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,19 +1298,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,12 +1315,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122407709</v>
+        <v>122406658</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454420</v>
+        <v>454390</v>
       </c>
       <c r="R3" t="n">
-        <v>6754420</v>
+        <v>6754454</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,14 +860,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på äldre sälg.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122406658</v>
+        <v>122409149</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,37 +915,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454390</v>
+        <v>454455</v>
       </c>
       <c r="R4" t="n">
-        <v>6754454</v>
+        <v>6754359</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,19 +977,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,12 +994,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122408664</v>
+        <v>122407709</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,37 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454418</v>
+        <v>454420</v>
       </c>
       <c r="R6" t="n">
-        <v>6754374</v>
+        <v>6754420</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,19 +1181,14 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:08</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122409149</v>
+        <v>122408664</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,42 +1231,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454455</v>
+        <v>454418</v>
       </c>
       <c r="R7" t="n">
-        <v>6754359</v>
+        <v>6754374</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,9 +1288,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,12 +1315,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122408531</v>
+        <v>122406658</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454354</v>
+        <v>454390</v>
       </c>
       <c r="R2" t="n">
-        <v>6754279</v>
+        <v>6754454</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122406658</v>
+        <v>122407709</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454390</v>
+        <v>454420</v>
       </c>
       <c r="R3" t="n">
-        <v>6754454</v>
+        <v>6754420</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +860,14 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:44</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122409149</v>
+        <v>122408874</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,29 +910,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långsisdammen, Dlr</t>
@@ -1006,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122408874</v>
+        <v>122409149</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,24 +1012,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsisdammen, Dlr</t>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122407709</v>
+        <v>122408664</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,37 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454420</v>
+        <v>454418</v>
       </c>
       <c r="R6" t="n">
-        <v>6754420</v>
+        <v>6754374</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,14 +1176,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lunglav på äldre sälg.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122408664</v>
+        <v>122408531</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454418</v>
+        <v>454354</v>
       </c>
       <c r="R7" t="n">
-        <v>6754374</v>
+        <v>6754279</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1315,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410135</v>
+        <v>122410095</v>
       </c>
       <c r="B8" t="n">
-        <v>56593</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,49 +1339,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454406</v>
+        <v>454463</v>
       </c>
       <c r="R8" t="n">
-        <v>6754542</v>
+        <v>6754144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1417,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,22 +1437,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122410095</v>
+        <v>122410135</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>56594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,46 +1461,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454463</v>
+        <v>454406</v>
       </c>
       <c r="R9" t="n">
-        <v>6754144</v>
+        <v>6754542</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,12 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122406658</v>
+        <v>122408874</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454390</v>
+        <v>454455</v>
       </c>
       <c r="R2" t="n">
-        <v>6754454</v>
+        <v>6754359</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +780,7 @@
         <v>122407709</v>
       </c>
       <c r="B3" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122408874</v>
+        <v>122406658</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R4" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,9 +957,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122409149</v>
+        <v>122408664</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,42 +1012,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454455</v>
+        <v>454418</v>
       </c>
       <c r="R5" t="n">
-        <v>6754359</v>
+        <v>6754374</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,9 +1069,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122408664</v>
+        <v>122409149</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,37 +1124,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454418</v>
+        <v>454455</v>
       </c>
       <c r="R6" t="n">
-        <v>6754374</v>
+        <v>6754359</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,19 +1186,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,12 +1203,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>122408531</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122408874</v>
+        <v>122407517</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454455</v>
+        <v>454420</v>
       </c>
       <c r="R2" t="n">
-        <v>6754359</v>
+        <v>6754420</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lunglav på äldre sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122407709</v>
+        <v>122408531</v>
       </c>
       <c r="B3" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454420</v>
+        <v>454354</v>
       </c>
       <c r="R3" t="n">
-        <v>6754420</v>
+        <v>6754279</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +855,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på äldre sälg.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,19 +882,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122406658</v>
+        <v>122408874</v>
       </c>
       <c r="B4" t="n">
         <v>78660</v>
@@ -920,17 +930,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454390</v>
+        <v>454455</v>
       </c>
       <c r="R4" t="n">
-        <v>6754454</v>
+        <v>6754359</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +967,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122408531</v>
+        <v>122406658</v>
       </c>
       <c r="B7" t="n">
         <v>78660</v>
@@ -1251,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454354</v>
+        <v>454390</v>
       </c>
       <c r="R7" t="n">
-        <v>6754279</v>
+        <v>6754454</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122409149</v>
+        <v>122406658</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,42 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454455</v>
+        <v>454390</v>
       </c>
       <c r="R6" t="n">
-        <v>6754359</v>
+        <v>6754454</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,9 +1181,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122406658</v>
+        <v>122410135</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,38 +1232,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454390</v>
+        <v>454406</v>
       </c>
       <c r="R7" t="n">
-        <v>6754454</v>
+        <v>6754542</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410095</v>
+        <v>122409149</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,22 +1376,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454463</v>
+        <v>454455</v>
       </c>
       <c r="R8" t="n">
-        <v>6754144</v>
+        <v>6754359</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,24 +1418,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,22 +1435,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122410135</v>
+        <v>122410095</v>
       </c>
       <c r="B9" t="n">
-        <v>56594</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,49 +1459,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454406</v>
+        <v>454463</v>
       </c>
       <c r="R9" t="n">
-        <v>6754542</v>
+        <v>6754144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1537,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -1340,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122409149</v>
+        <v>122410095</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1376,22 +1376,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454455</v>
+        <v>454463</v>
       </c>
       <c r="R8" t="n">
-        <v>6754359</v>
+        <v>6754144</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,9 +1418,24 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,19 +1450,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122410095</v>
+        <v>122409149</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1483,22 +1498,22 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454463</v>
+        <v>454455</v>
       </c>
       <c r="R9" t="n">
-        <v>6754144</v>
+        <v>6754359</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,24 +1540,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -1340,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410095</v>
+        <v>122409149</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1376,22 +1376,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454463</v>
+        <v>454455</v>
       </c>
       <c r="R8" t="n">
-        <v>6754144</v>
+        <v>6754359</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,24 +1418,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,19 +1435,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122409149</v>
+        <v>122410095</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1498,22 +1483,22 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454455</v>
+        <v>454463</v>
       </c>
       <c r="R9" t="n">
-        <v>6754359</v>
+        <v>6754144</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,9 +1525,24 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -1343,7 +1343,7 @@
         <v>122410095</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>122409149</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 894-2025 artfynd.xlsx
+++ b/artfynd/A 894-2025 artfynd.xlsx
@@ -1340,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122410095</v>
+        <v>122409149</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1376,22 +1376,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454463</v>
+        <v>454455</v>
       </c>
       <c r="R8" t="n">
-        <v>6754144</v>
+        <v>6754359</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,24 +1418,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,19 +1435,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122409149</v>
+        <v>122410095</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1498,22 +1483,22 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454455</v>
+        <v>454463</v>
       </c>
       <c r="R9" t="n">
-        <v>6754359</v>
+        <v>6754144</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,9 +1525,24 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
